--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="474">
   <si>
     <t>Filename</t>
   </si>
@@ -808,622 +808,634 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9809,0.0007,0.0059,0.0035</t>
-  </si>
-  <si>
-    <t>0.0044,0.0001,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.9800,0.0001,0.0000,0.0151</t>
-  </si>
-  <si>
-    <t>0.0571,0.0000,0.0000,0.9939</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9919,0.0013,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0727,0.0001,0.0000,0.9777</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.0007,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.9880,0.0003,0.0147,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.0007,0.9948,0.0010</t>
+  </si>
+  <si>
+    <t>0.9842,0.0006,0.0128,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0070,0.9927,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8352,0.0008,0.1496,0.0020</t>
+  </si>
+  <si>
+    <t>0.6115,0.0003,0.4416,0.0011</t>
+  </si>
+  <si>
+    <t>0.0027,0.0008,0.9962,0.0004</t>
+  </si>
+  <si>
+    <t>0.0118,0.0009,0.9883,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9833,0.0003,0.0156,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0098,0.7315,0.2387,0.0002</t>
+  </si>
+  <si>
+    <t>0.9530,0.0001,0.0406,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0406,0.9726,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9977,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0176,0.7824,0.1155,0.0010</t>
+  </si>
+  <si>
+    <t>0.0036,0.0002,0.9932,0.0015</t>
+  </si>
+  <si>
+    <t>0.0064,0.0035,0.9862,0.0033</t>
+  </si>
+  <si>
+    <t>0.0110,0.0002,0.9894,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0027,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.1096,0.0000,0.9564</t>
+  </si>
+  <si>
+    <t>0.0040,0.9925,0.0017,0.0043</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0029,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.1318,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9982,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9988,0.0015</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0009,0.0001</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0016,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0005,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.9428,0.0002,0.1009,0.0000</t>
-  </si>
-  <si>
-    <t>0.3920,0.0013,0.6188,0.0016</t>
-  </si>
-  <si>
-    <t>0.9974,0.0004,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.9978,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8133,0.0005,0.1371,0.0078</t>
-  </si>
-  <si>
-    <t>0.0611,0.0013,0.9419,0.0009</t>
-  </si>
-  <si>
-    <t>0.1284,0.0004,0.9398,0.0000</t>
-  </si>
-  <si>
-    <t>0.0072,0.0007,0.9913,0.0008</t>
-  </si>
-  <si>
-    <t>0.0140,0.0002,0.9890,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0018,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0007,0.0055,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0119,0.9660,0.0105,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0030,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3476,0.7294,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9985,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0075,0.3938,0.5156,0.0002</t>
-  </si>
-  <si>
-    <t>0.0907,0.0003,0.8347,0.0107</t>
-  </si>
-  <si>
-    <t>0.0024,0.0018,0.9942,0.0010</t>
-  </si>
-  <si>
-    <t>0.0083,0.0000,0.9839,0.0021</t>
-  </si>
-  <si>
-    <t>0.0013,0.0038,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9984,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0978,0.0000,0.9785</t>
-  </si>
-  <si>
-    <t>0.0067,0.9948,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0121,0.0000</t>
+    <t>0.0004,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.9769,0.0282,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.8184,0.9923,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0018,0.9979,0.0004</t>
+  </si>
+  <si>
+    <t>0.0034,0.0136,0.9746,0.0154</t>
+  </si>
+  <si>
+    <t>0.0000,0.9753,0.9879,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9993,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9993,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9615,0.0007,0.0356,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9360,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9626,0.9049,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9918,0.9811,0.0000</t>
+  </si>
+  <si>
+    <t>0.0056,0.0009,0.0023,0.9953</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0002,0.0005,0.9988</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0149,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9684,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9929,0.0164,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9163,0.8949,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9541,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9063,0.9916,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0071,0.0010,0.9925,0.0003</t>
+  </si>
+  <si>
+    <t>0.9927,0.0003,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0048,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0398,0.9925,0.0014</t>
-  </si>
-  <si>
-    <t>0.0046,0.0006,0.9929,0.0008</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0888,0.0002,0.9530,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0005,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0018,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0006,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9777,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0035,0.0044,0.9925,0.0022</t>
-  </si>
-  <si>
-    <t>0.0001,0.9321,0.9858,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.9980,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.9988,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9442,0.0002,0.0949,0.0002</t>
-  </si>
-  <si>
-    <t>0.6805,0.0012,0.3631,0.0019</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9447,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9670,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9984,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.6220,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.0001,0.0023,0.9969</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.0005,0.9992</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9866,0.9721,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8902,0.9925,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.6301,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.6311,0.8036,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9095,0.9873,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
+    <t>0.1270,0.9014,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0011,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.8109,0.0002,0.3328,0.0000</t>
+  </si>
+  <si>
+    <t>0.8128,0.0580,0.0323,0.0012</t>
+  </si>
+  <si>
+    <t>0.3749,0.0009,0.6772,0.0002</t>
+  </si>
+  <si>
+    <t>0.0075,0.0174,0.0012,0.9883</t>
+  </si>
+  <si>
+    <t>0.0011,0.9990,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9848,0.9131,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9453,0.0652,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9754,0.0300,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.3745,0.9615,0.0007</t>
+  </si>
+  <si>
+    <t>0.0138,0.0031,0.9865,0.0000</t>
+  </si>
+  <si>
+    <t>0.8629,0.0006,0.1681,0.0000</t>
+  </si>
+  <si>
+    <t>0.0098,0.0136,0.9721,0.0012</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.1768,0.0005,0.8610,0.0015</t>
+  </si>
+  <si>
+    <t>0.9933,0.0011,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0152,0.0001,0.0000,0.9903</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9954,0.9017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.9957,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8731,0.1704,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.1631,0.0000,0.0000,0.9912</t>
+  </si>
+  <si>
+    <t>0.0007,0.0134,0.9975,0.0028</t>
+  </si>
+  <si>
+    <t>0.9971,0.0000,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0309,0.9572,0.0107,0.0010</t>
+  </si>
+  <si>
+    <t>0.9903,0.0051,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.3088,0.5860,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9336,0.0317,0.0083,0.0022</t>
+  </si>
+  <si>
+    <t>0.9936,0.0028,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9513,0.0737,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6008,0.5188,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.3948,0.7168,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.0353,0.0148,0.9722,0.0008</t>
+  </si>
+  <si>
+    <t>0.9967,0.0035,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0022,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0020,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.3656,0.0015,0.6393,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.0001,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0518,0.0067,0.9289,0.0045</t>
+  </si>
+  <si>
+    <t>0.0035,0.0011,0.9942,0.0013</t>
+  </si>
+  <si>
+    <t>0.5407,0.0119,0.4096,0.0036</t>
+  </si>
+  <si>
+    <t>0.9732,0.0021,0.0182,0.0002</t>
+  </si>
+  <si>
+    <t>0.5602,0.2146,0.0366,0.0003</t>
+  </si>
+  <si>
+    <t>0.2683,0.0038,0.7037,0.0002</t>
+  </si>
+  <si>
+    <t>0.6066,0.0010,0.3780,0.0035</t>
+  </si>
+  <si>
+    <t>0.0892,0.0020,0.9229,0.0036</t>
+  </si>
+  <si>
+    <t>0.3255,0.7657,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0384,0.9751,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9907,0.0150,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9903,0.0105,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.6350,0.4287,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9291,0.0158,0.0149,0.0021</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.3223,0.2488,0.0875,0.0208</t>
+  </si>
+  <si>
+    <t>0.9910,0.0004,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.0752,0.0006,0.9494,0.0024</t>
+  </si>
+  <si>
+    <t>0.0120,0.0007,0.9870,0.0002</t>
+  </si>
+  <si>
+    <t>0.4224,0.0092,0.5274,0.0007</t>
+  </si>
+  <si>
+    <t>0.6071,0.0011,0.3922,0.0003</t>
+  </si>
+  <si>
+    <t>0.0101,0.0126,0.9718,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0019,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0005</t>
+  </si>
+  <si>
+    <t>0.0147,0.8048,0.1995,0.0007</t>
+  </si>
+  <si>
+    <t>0.8693,0.0007,0.1518,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.0032,0.9931,0.0007</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0007,0.0002,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.9916,0.0003,0.0021,0.0009</t>
-  </si>
-  <si>
-    <t>0.0068,0.0000,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8666,0.1941,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8271,0.0101,0.1274,0.0104</t>
-  </si>
-  <si>
-    <t>0.1403,0.0029,0.8626,0.0002</t>
-  </si>
-  <si>
-    <t>0.5293,0.3231,0.0122,0.0012</t>
-  </si>
-  <si>
-    <t>0.8553,0.0015,0.1483,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0005,0.0012,0.9980</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0067,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9955,0.7110,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.9987,0.0030,0.0000</t>
-  </si>
-  <si>
-    <t>0.9802,0.0192,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9290,0.0760,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.2715,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0057,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0011,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0078,0.0484,0.9490,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0003,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.2359,0.0002,0.8699,0.0003</t>
-  </si>
-  <si>
-    <t>0.9220,0.0043,0.0546,0.0024</t>
-  </si>
-  <si>
-    <t>0.0857,0.0000,0.0000,0.9793</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9830,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0073,0.9889,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.7456,0.3401,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4351,0.0000,0.0000,0.9662</t>
-  </si>
-  <si>
-    <t>0.0002,0.0103,0.9994,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.0287,0.9769,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.1122,0.8592,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9807,0.0272,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7445,0.3348,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.5195,0.6005,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0029,0.9975,0.0002</t>
-  </si>
-  <si>
-    <t>0.9764,0.0369,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0016,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9842,0.0089,0.0047,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0037,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0187,0.0038,0.9755,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.0890,0.9661,0.0060</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.7930,0.0023,0.1913,0.0041</t>
-  </si>
-  <si>
-    <t>0.2405,0.0144,0.6598,0.0004</t>
-  </si>
-  <si>
-    <t>0.4511,0.1123,0.1308,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0003,0.0069,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0002,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.8860,0.0011,0.0882,0.0108</t>
-  </si>
-  <si>
-    <t>0.0229,0.9852,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0091,0.9909,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.9385,0.0940,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0060,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8833,0.1545,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9556,0.0218,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9945,0.0003,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0600,0.9139,0.0060,0.0045</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0236,0.0012,0.9836,0.0019</t>
-  </si>
-  <si>
-    <t>0.0065,0.0168,0.9764,0.0008</t>
-  </si>
-  <si>
-    <t>0.0307,0.0014,0.9736,0.0004</t>
-  </si>
-  <si>
-    <t>0.1326,0.0001,0.9367,0.0000</t>
-  </si>
-  <si>
-    <t>0.0200,0.0093,0.9601,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0018,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.0164,0.3613,0.8216,0.0015</t>
-  </si>
-  <si>
-    <t>0.5002,0.0014,0.5099,0.0006</t>
-  </si>
-  <si>
-    <t>0.0112,0.0001,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0041,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.0048,0.0002,0.9948,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0095,0.0011,0.9841,0.0031</t>
-  </si>
-  <si>
-    <t>0.8680,0.0001,0.1692,0.0006</t>
-  </si>
-  <si>
-    <t>0.9966,0.0000,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0018,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0008,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.0021,0.9926,0.0007</t>
-  </si>
-  <si>
-    <t>0.0019,0.0096,0.9871,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.3419,0.0003,0.6933,0.0032</t>
-  </si>
-  <si>
-    <t>0.0178,0.0011,0.9729,0.0024</t>
-  </si>
-  <si>
-    <t>0.0089,0.0012,0.9811,0.0034</t>
-  </si>
-  <si>
-    <t>0.8349,0.0000,0.0002,0.5303</t>
-  </si>
-  <si>
-    <t>0.0005,0.0030,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0004,0.9995</t>
-  </si>
-  <si>
-    <t>0.7533,0.0003,0.0001,0.3302</t>
+    <t>0.0007,0.0002,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0020,0.9992,0.0012</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0000,0.0057,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9946,0.0048,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.3269,0.0019,0.7076,0.0001</t>
+  </si>
+  <si>
+    <t>0.0037,0.0001,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0541,0.9483,0.0014</t>
+  </si>
+  <si>
+    <t>0.0119,0.0080,0.9730,0.0034</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.8539,0.0002,0.1193,0.0059</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9935,0.0102</t>
+  </si>
+  <si>
+    <t>0.1265,0.0007,0.8058,0.0125</t>
+  </si>
+  <si>
+    <t>0.9867,0.0000,0.0002,0.0356</t>
+  </si>
+  <si>
+    <t>0.0002,0.0252,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0030,0.0000,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.9930,0.0001,0.0000,0.0056</t>
   </si>
 </sst>
 </file>
@@ -1809,7 +1821,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1823,7 +1835,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1837,7 +1849,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1851,7 +1863,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1865,7 +1877,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1879,7 +1891,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1893,7 +1905,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1907,7 +1919,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1921,7 +1933,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1935,7 +1947,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1949,7 +1961,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1963,7 +1975,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1977,7 +1989,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1991,7 +2003,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2005,7 +2017,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2019,7 +2031,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2033,7 +2045,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2047,7 +2059,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2061,7 +2073,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2075,7 +2087,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2089,7 +2101,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2103,7 +2115,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2117,7 +2129,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2128,10 +2140,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2145,7 +2157,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2159,7 +2171,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2173,7 +2185,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2187,7 +2199,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2201,7 +2213,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2215,7 +2227,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2229,7 +2241,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2243,7 +2255,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2257,7 +2269,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2271,7 +2283,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2285,7 +2297,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2299,7 +2311,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2313,7 +2325,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2324,10 +2336,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2341,7 +2353,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2355,7 +2367,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2369,7 +2381,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2383,7 +2395,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2397,7 +2409,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2411,7 +2423,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2425,7 +2437,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2439,7 +2451,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2453,7 +2465,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2467,7 +2479,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2481,7 +2493,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2495,7 +2507,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2509,7 +2521,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2523,7 +2535,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2537,7 +2549,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2551,7 +2563,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2565,7 +2577,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2579,7 +2591,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2593,7 +2605,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2607,7 +2619,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2621,7 +2633,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2635,7 +2647,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2649,7 +2661,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2663,7 +2675,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2677,7 +2689,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2691,7 +2703,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2705,7 +2717,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2719,7 +2731,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2733,7 +2745,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2747,7 +2759,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2761,7 +2773,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2775,7 +2787,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2789,7 +2801,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2803,7 +2815,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2817,7 +2829,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2831,7 +2843,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2845,7 +2857,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2859,7 +2871,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2873,7 +2885,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2887,7 +2899,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2901,7 +2913,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2915,7 +2927,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2929,7 +2941,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2940,10 +2952,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2957,7 +2969,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2968,10 +2980,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2985,7 +2997,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2999,7 +3011,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3013,7 +3025,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3027,7 +3039,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3041,7 +3053,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3055,7 +3067,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3069,7 +3081,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3083,7 +3095,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3097,7 +3109,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3111,7 +3123,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3125,7 +3137,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3139,7 +3151,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3153,7 +3165,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3167,7 +3179,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3181,7 +3193,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3195,7 +3207,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3209,7 +3221,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3223,7 +3235,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3237,7 +3249,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3251,7 +3263,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3265,7 +3277,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3279,7 +3291,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3293,7 +3305,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3307,7 +3319,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3321,7 +3333,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3335,7 +3347,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3349,7 +3361,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3363,7 +3375,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3377,7 +3389,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>282</v>
+        <v>361</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3388,10 +3400,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3405,7 +3417,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3416,10 +3428,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3433,7 +3445,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3444,10 +3456,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3461,7 +3473,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3475,7 +3487,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3489,7 +3501,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>366</v>
+        <v>305</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3503,7 +3515,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3517,7 +3529,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3531,7 +3543,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3545,7 +3557,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3559,7 +3571,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3573,7 +3585,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3587,7 +3599,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3601,7 +3613,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3615,7 +3627,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3629,7 +3641,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3643,7 +3655,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3657,7 +3669,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>268</v>
+        <v>374</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3671,7 +3683,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3685,7 +3697,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3699,7 +3711,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3710,10 +3722,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D138" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3727,7 +3739,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3741,7 +3753,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3755,7 +3767,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3769,7 +3781,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3783,7 +3795,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3797,7 +3809,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3811,7 +3823,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3825,7 +3837,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>382</v>
+        <v>338</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3839,7 +3851,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>339</v>
+        <v>384</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3853,7 +3865,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3867,7 +3879,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3881,7 +3893,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3895,7 +3907,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3909,7 +3921,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3923,7 +3935,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3937,7 +3949,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3951,7 +3963,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3965,7 +3977,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3979,7 +3991,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3993,7 +4005,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4007,7 +4019,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4021,7 +4033,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4035,7 +4047,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4049,7 +4061,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4063,7 +4075,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4077,7 +4089,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4091,7 +4103,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4105,7 +4117,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>268</v>
+        <v>401</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4119,7 +4131,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>319</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4133,7 +4145,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>399</v>
+        <v>319</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4147,7 +4159,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4161,7 +4173,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4175,7 +4187,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4189,7 +4201,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4203,7 +4215,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4214,10 +4226,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4231,7 +4243,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4245,7 +4257,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4259,7 +4271,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4273,7 +4285,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4287,7 +4299,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4301,7 +4313,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4315,7 +4327,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4329,7 +4341,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4343,7 +4355,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4357,7 +4369,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4371,7 +4383,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>350</v>
+        <v>415</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4385,7 +4397,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4399,7 +4411,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4413,7 +4425,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4427,7 +4439,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4441,7 +4453,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4455,7 +4467,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4469,7 +4481,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4480,10 +4492,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4497,7 +4509,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4508,10 +4520,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4525,7 +4537,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4536,10 +4548,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4553,7 +4565,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4567,7 +4579,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4581,7 +4593,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4595,7 +4607,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4609,7 +4621,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4623,7 +4635,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4637,7 +4649,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4651,7 +4663,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4662,10 +4674,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4679,7 +4691,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4693,7 +4705,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4707,7 +4719,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4721,7 +4733,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4732,10 +4744,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4749,7 +4761,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4763,7 +4775,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4777,7 +4789,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4791,7 +4803,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>319</v>
+        <v>444</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4805,7 +4817,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4819,7 +4831,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4833,7 +4845,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4847,7 +4859,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>269</v>
+        <v>386</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4861,7 +4873,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4875,7 +4887,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4886,10 +4898,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4900,10 +4912,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4917,7 +4929,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>447</v>
+        <v>320</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4931,7 +4943,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>409</v>
+        <v>451</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4945,7 +4957,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4959,7 +4971,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4973,7 +4985,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4987,7 +4999,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>350</v>
+        <v>455</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5001,7 +5013,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5015,7 +5027,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5029,7 +5041,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5043,7 +5055,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5057,7 +5069,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5085,7 +5097,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>455</v>
+        <v>271</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5099,7 +5111,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>456</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5113,7 +5125,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5127,7 +5139,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5141,7 +5153,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>455</v>
+        <v>271</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5155,7 +5167,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>346</v>
+        <v>271</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5169,7 +5181,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5183,7 +5195,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5197,7 +5209,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5211,7 +5223,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5225,7 +5237,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5239,7 +5251,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5250,10 +5262,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5267,7 +5279,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5281,7 +5293,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5292,10 +5304,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5309,7 +5321,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5323,7 +5335,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5337,7 +5349,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5351,7 +5363,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5365,7 +5377,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
